--- a/output/ai-shinryou-db/text/2026/hosei-tsuuchi-i/2026_別添２（医科診療所用）［70KB］_20260501.xlsx
+++ b/output/ai-shinryou-db/text/2026/hosei-tsuuchi-i/2026_別添２（医科診療所用）［70KB］_20260501.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="121" documentId="13_ncr:1_{A768D5E5-1730-4002-8CCB-C24C4BC98C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3469C841-7E44-4127-92E8-60CAB8696E34}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{BC039FBE-0D9C-40F4-9074-82F8CC533331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15F43EE8-8683-4402-A0AD-72F85A43C2AE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F6229C59-2DDD-48CB-913F-EF8B6B1215DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{F6229C59-2DDD-48CB-913F-EF8B6B1215DB}"/>
   </bookViews>
   <sheets>
     <sheet name="チェックリストの利用方法" sheetId="1" r:id="rId1"/>
@@ -13,8 +13,8 @@
     <sheet name="リスト" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">【医科診療所用】チェックリスト!$A$10:$J$78</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">【医科診療所用】チェックリスト!$B$1:$I$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">【医科診療所用】チェックリスト!$A$10:$J$79</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">【医科診療所用】チェックリスト!$B$1:$I$80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">【医科診療所用】チェックリスト!$1:$10</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="114">
   <si>
     <t>チェックリストの利用方法　　　　　　</t>
     <rPh sb="8" eb="10">
@@ -499,6 +499,14 @@
     <t>□</t>
   </si>
   <si>
+    <t>初診料（医科）の注16に規定する電子的診療情報連携体制整備加算１並びに再診料（医科）の注19及び外来診療料の注10に規定する電子的診療情報連携体制整備加算</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>初診料（医科）の注16に規定する電子的診療情報連携体制整備加算２並びに再診料（医科）の注19及び外来診療料の注10に規定する電子的診療情報連携体制整備加算</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
     <t>初診料（医科）の注16に規定する電子的診療情報連携体制整備加算３並びに再診料（医科）の注19及び外来診療料の注10に規定する電子的診療情報連携体制整備加算</t>
     <rPh sb="32" eb="33">
       <t>ナラ</t>
@@ -506,14 +514,38 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
+    <t>継続的に賃上げに係る取組を実施している保険医療機関の基準（入院料減算免除）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>外来・在宅ベースアップ評価料（Ⅰ）の注５等に係る届出（項番51）と同一の様式で届出可能</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>外来データ提出加算</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>地域包括診療加算</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>口腔管理連携加算</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「Ａ２０７－５」電子的診療情報連携体制整備加算１</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
     <t>有床診療所入院基本料及び有床診療所療養病床入院基本料</t>
   </si>
   <si>
-    <t>地域包括診療加算</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>口腔管理連携加算</t>
+    <t>「Ａ２０７－５」電子的診療情報連携体制整備加算２</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>身体的拘束最小化推進体制加算</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -618,6 +650,10 @@
     <t>別添１の「第９」の２の（３）に規定する在宅医療充実体制加算</t>
   </si>
   <si>
+    <t>在宅時医学総合管理料の注 16（施設入居時等医学総合管理料の注５の規定により準用する場合を含む。）に規定する基準に該当しない場合に限る。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
     <t>救急患者連携搬送料</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -655,6 +691,10 @@
     <t>ポジトロン断層・磁気共鳴コンピューター断層複合撮影（ＰＳＭＡイメージング剤を用いた場合に限る。）</t>
   </si>
   <si>
+    <t>地域支援・外来医薬品供給対応体制加算</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
     <t>通院・在宅精神療法の注９に規定する心理支援加算</t>
   </si>
   <si>
@@ -675,6 +715,10 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
+    <t>人工膝関節置換術（手術支援装置を用いるもの）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
     <t>吸入麻酔又は静脈麻酔による深鎮静（声門上器具又は気管挿管による気道確保を伴わないもの）１</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -685,6 +729,17 @@
     <t>国際標準病理診断管理加算</t>
   </si>
   <si>
+    <t>継続的に賃上げに係る取組を実施している保険医療機関の基準（外来・在宅ベースアップ評価料（Ⅰ）の注５等）</t>
+    <rPh sb="0" eb="2">
+      <t>ケイゾク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>入院料減算免除に係る届出（項番４）と同一の様式で届出可能</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
     <t>外来・在宅ベースアップ評価料（Ｉ）の注５</t>
   </si>
   <si>
@@ -695,80 +750,6 @@
   </si>
   <si>
     <t>別添１の「第９」の１の（１）に規定する在宅療養支援診療所</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>別添１の「第９」の１の（２）のイに規定する在宅療養支援診療所</t>
-  </si>
-  <si>
-    <t>別添１の「第９」の１の（３）に規定する在宅療養支援診療所</t>
-  </si>
-  <si>
-    <t>ＣＴ撮影及びＭＲＩ撮影</t>
-  </si>
-  <si>
-    <t>128 列以上のマルチスライス型の機器によるＣＴ撮影に限る。</t>
-  </si>
-  <si>
-    <t>通院・在宅精神療法の注11に規定する早期診療体制充実加算１</t>
-  </si>
-  <si>
-    <t>通院・在宅精神療法の注11に規定する早期診療体制充実加算３</t>
-  </si>
-  <si>
-    <t>医科点数表第２章第９部処置の通則の５に掲げる処置の休日加算１</t>
-  </si>
-  <si>
-    <t>医科点数表第２章第９部処置の通則の５に掲げる処置の時間外加算１</t>
-  </si>
-  <si>
-    <t>医科点数表第２章第９部処置の通則の５に掲げる処置の深夜加算１</t>
-  </si>
-  <si>
-    <t>外来・在宅ベースアップ評価料（Ｉ）</t>
-  </si>
-  <si>
-    <t>外来・在宅ベースアップ評価料（Ⅱ）（１～24）</t>
-  </si>
-  <si>
-    <t>入院ベースアップ評価料（１～500）</t>
-  </si>
-  <si>
-    <t>ＢＲＣＡ１／２遺伝子検査の腫瘍細胞を検体とするもの</t>
-  </si>
-  <si>
-    <t>乳癌患者に対して、抗悪性腫瘍剤による治療法の選択を目的として検査を実施する場合に限る。</t>
-  </si>
-  <si>
-    <t>在宅時医学総合管理料及び施設入居時等医学総合管理料</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>☑</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>□</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>人工膝関節置換術（手術支援装置を用いるもの）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>外来データ提出加算</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>身体的拘束最小化推進体制加算</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>初診料（医科）の注16に規定する電子的診療情報連携体制整備加算１並びに再診料（医科）の注19及び外来診療料の注10に規定する電子的診療情報連携体制整備加算</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>初診料（医科）の注16に規定する電子的診療情報連携体制整備加算２並びに再診料（医科）の注19及び外来診療料の注10に規定する電子的診療情報連携体制整備加算</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -800,34 +781,61 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
+    <t>別添１の「第９」の１の（２）のイに規定する在宅療養支援診療所</t>
+  </si>
+  <si>
     <t>令和８年３月31日において現に在宅療養支援診療所の届出を行っている保険医療機関については、業務継続計画に係る施設基準を満たした上で、令和９年６月１日以降に引き続き届け出る場合に限る。</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>「Ａ２０７－５」電子的診療情報連携体制整備加算１</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>「Ａ２０７－５」電子的診療情報連携体制整備加算２</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>継続的に賃上げに係る取組を実施している保険医療機関の基準（外来・在宅ベースアップ評価料（Ⅰ）の注５等）</t>
-    <rPh sb="0" eb="2">
-      <t>ケイゾク</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>入院料減算免除に係る届出（項番４）と同一の様式で届出可能</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>外来・在宅ベースアップ評価料（Ⅰ）の注５等に係る届出（項番51）と同一の様式で届出可能</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>継続的に賃上げに係る取組を実施している保険医療機関の基準（入院料減算免除）</t>
+    <t>別添１の「第９」の１の（３）に規定する在宅療養支援診療所</t>
+  </si>
+  <si>
+    <t>ＣＴ撮影及びＭＲＩ撮影</t>
+  </si>
+  <si>
+    <t>128 列以上のマルチスライス型の機器によるＣＴ撮影に限る。</t>
+  </si>
+  <si>
+    <t>通院・在宅精神療法の注11に規定する早期診療体制充実加算１</t>
+  </si>
+  <si>
+    <t>通院・在宅精神療法の注11に規定する早期診療体制充実加算３</t>
+  </si>
+  <si>
+    <t>医科点数表第２章第９部処置の通則の５に掲げる処置の休日加算１</t>
+  </si>
+  <si>
+    <t>医科点数表第２章第９部処置の通則の５に掲げる処置の時間外加算１</t>
+  </si>
+  <si>
+    <t>医科点数表第２章第９部処置の通則の５に掲げる処置の深夜加算１</t>
+  </si>
+  <si>
+    <t>外来・在宅ベースアップ評価料（Ｉ）</t>
+  </si>
+  <si>
+    <t>外来・在宅ベースアップ評価料（Ⅱ）（１～24）</t>
+  </si>
+  <si>
+    <t>入院ベースアップ評価料（１～500）</t>
+  </si>
+  <si>
+    <t>ＢＲＣＡ１／２遺伝子検査の腫瘍細胞を検体とするもの</t>
+  </si>
+  <si>
+    <t>乳癌患者に対して、抗悪性腫瘍剤による治療法の選択を目的として検査を実施する場合に限る。</t>
+  </si>
+  <si>
+    <t>☑</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>□</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>在宅時医学総合管理料の注 16（施設入居時等医学総合管理料の注５の規定により準用する場合を含む。）に規定する基準</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -838,7 +846,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@" x16r2:formatCode16="[$-ja-JP-x-gannen]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1064,6 +1072,14 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1248,7 +1264,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1353,6 +1369,63 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="23" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1362,83 +1435,8 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="23" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2264,24 +2262,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
@@ -2345,10 +2343,10 @@
     <tabColor rgb="FF00B050"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.625" style="9" customWidth="1"/>
     <col min="3" max="3" width="15.375" style="9" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" customWidth="1"/>
@@ -2362,23 +2360,23 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="H3" s="12" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="13">
-        <v>46132</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
@@ -2387,16 +2385,16 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
     </row>
     <row r="6" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="15" t="s">
@@ -2404,16 +2402,16 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="63" t="s">
+      <c r="B7" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C8" s="15"/>
@@ -2428,49 +2426,49 @@
       </c>
     </row>
     <row r="10" spans="1:10" s="16" customFormat="1" ht="40.5" x14ac:dyDescent="0.4">
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="49" t="s">
+      <c r="D10" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="49" t="s">
+      <c r="E10" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="49" t="s">
+      <c r="F10" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="49" t="s">
+      <c r="G10" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="49" t="s">
+      <c r="H10" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="50" t="s">
+      <c r="I10" s="45" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="27" x14ac:dyDescent="0.4">
-      <c r="B11" s="39">
+      <c r="B11" s="36">
         <v>1</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="37">
         <v>46174</v>
       </c>
       <c r="D11" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="38" t="s">
         <v>25</v>
       </c>
       <c r="F11" s="33" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="H11" s="33" t="s">
         <v>26</v>
@@ -2479,23 +2477,23 @@
       <c r="J11" s="9"/>
     </row>
     <row r="12" spans="1:10" ht="27" x14ac:dyDescent="0.4">
-      <c r="B12" s="39">
+      <c r="B12" s="36">
         <v>2</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="37">
         <v>46174</v>
       </c>
       <c r="D12" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="38" t="s">
         <v>25</v>
       </c>
       <c r="F12" s="33" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="H12" s="33" t="s">
         <v>26</v>
@@ -2504,23 +2502,23 @@
       <c r="J12" s="9"/>
     </row>
     <row r="13" spans="1:10" ht="27" x14ac:dyDescent="0.4">
-      <c r="B13" s="39">
+      <c r="B13" s="36">
         <v>3</v>
       </c>
-      <c r="C13" s="40">
+      <c r="C13" s="37">
         <v>46174</v>
       </c>
       <c r="D13" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="38" t="s">
         <v>25</v>
       </c>
       <c r="F13" s="33" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H13" s="33" t="s">
         <v>26</v>
@@ -2530,33 +2528,33 @@
     </row>
     <row r="14" spans="1:10" s="21" customFormat="1" ht="40.5" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
-      <c r="B14" s="39">
+      <c r="B14" s="36">
         <v>4</v>
       </c>
-      <c r="C14" s="40">
+      <c r="C14" s="37">
         <v>46174</v>
       </c>
       <c r="D14" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="38" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="58" t="s">
-        <v>111</v>
-      </c>
-      <c r="H14" s="59" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="60" t="s">
-        <v>110</v>
+      <c r="G14" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="25" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B15" s="39">
+      <c r="B15" s="36">
         <v>5</v>
       </c>
       <c r="C15" s="23">
@@ -2565,25 +2563,25 @@
       <c r="D15" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="42" t="s">
+      <c r="E15" s="38" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="52" t="s">
-        <v>100</v>
+      <c r="G15" s="34" t="s">
+        <v>32</v>
       </c>
       <c r="H15" s="33" t="s">
         <v>26</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J15" s="9"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B16" s="39">
+      <c r="B16" s="36">
         <v>6</v>
       </c>
       <c r="C16" s="23">
@@ -2592,14 +2590,14 @@
       <c r="D16" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="E16" s="39" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H16" s="24" t="s">
         <v>26</v>
@@ -2608,7 +2606,7 @@
       <c r="J16" s="9"/>
     </row>
     <row r="17" spans="1:10" ht="27" x14ac:dyDescent="0.4">
-      <c r="B17" s="39">
+      <c r="B17" s="36">
         <v>7</v>
       </c>
       <c r="C17" s="23">
@@ -2617,25 +2615,25 @@
       <c r="D17" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="43" t="s">
+      <c r="E17" s="39" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="26" t="s">
-        <v>106</v>
+        <v>35</v>
       </c>
       <c r="H17" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J17" s="9"/>
     </row>
     <row r="18" spans="1:10" ht="27" x14ac:dyDescent="0.4">
-      <c r="B18" s="39">
+      <c r="B18" s="36">
         <v>8</v>
       </c>
       <c r="C18" s="23">
@@ -2644,95 +2642,95 @@
       <c r="D18" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="43" t="s">
+      <c r="E18" s="39" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="H18" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J18" s="9"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B19" s="39">
+      <c r="B19" s="36">
         <v>9</v>
       </c>
-      <c r="C19" s="40">
+      <c r="C19" s="37">
         <v>46174</v>
       </c>
       <c r="D19" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="42" t="s">
+      <c r="E19" s="38" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="33" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="H19" s="33" t="s">
         <v>26</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
-      <c r="B20" s="39">
+      <c r="B20" s="36">
         <v>10</v>
       </c>
-      <c r="C20" s="40">
+      <c r="C20" s="37">
         <v>46174</v>
       </c>
       <c r="D20" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="42" t="s">
+      <c r="E20" s="38" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="33" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H20" s="33" t="s">
         <v>26</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B21" s="39">
+      <c r="B21" s="36">
         <v>11</v>
       </c>
-      <c r="C21" s="40">
+      <c r="C21" s="37">
         <v>46539</v>
       </c>
       <c r="D21" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="45" t="s">
-        <v>34</v>
+      <c r="E21" s="41" t="s">
+        <v>42</v>
       </c>
       <c r="F21" s="33" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H21" s="33" t="s">
         <v>26</v>
@@ -2740,49 +2738,49 @@
       <c r="I21" s="25"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B22" s="39">
+      <c r="B22" s="36">
         <v>12</v>
       </c>
-      <c r="C22" s="40">
+      <c r="C22" s="37">
         <v>46539</v>
       </c>
       <c r="D22" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="45" t="s">
-        <v>34</v>
+      <c r="E22" s="41" t="s">
+        <v>42</v>
       </c>
       <c r="F22" s="33" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H22" s="33" t="s">
         <v>26</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B23" s="39">
+      <c r="B23" s="36">
         <v>13</v>
       </c>
       <c r="C23" s="23">
         <v>46174</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="38" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H23" s="24" t="s">
         <v>26</v>
@@ -2790,23 +2788,23 @@
       <c r="I23" s="25"/>
     </row>
     <row r="24" spans="1:10" ht="27" x14ac:dyDescent="0.4">
-      <c r="B24" s="39">
+      <c r="B24" s="36">
         <v>14</v>
       </c>
       <c r="C24" s="23">
         <v>46174</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="39" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="28" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H24" s="24" t="s">
         <v>26</v>
@@ -2814,23 +2812,23 @@
       <c r="I24" s="25"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B25" s="39">
+      <c r="B25" s="36">
         <v>15</v>
       </c>
       <c r="C25" s="23">
         <v>46174</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="39" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H25" s="24" t="s">
         <v>26</v>
@@ -2838,23 +2836,23 @@
       <c r="I25" s="25"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B26" s="39">
+      <c r="B26" s="36">
         <v>16</v>
       </c>
       <c r="C26" s="23">
         <v>46174</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="39" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="28" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H26" s="24" t="s">
         <v>26</v>
@@ -2862,23 +2860,23 @@
       <c r="I26" s="25"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B27" s="39">
+      <c r="B27" s="36">
         <v>17</v>
       </c>
       <c r="C27" s="23">
         <v>46174</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="39" t="s">
         <v>25</v>
       </c>
       <c r="F27" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H27" s="24" t="s">
         <v>26</v>
@@ -2886,23 +2884,23 @@
       <c r="I27" s="25"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B28" s="39">
+      <c r="B28" s="36">
         <v>18</v>
       </c>
       <c r="C28" s="23">
         <v>46174</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="39" t="s">
         <v>25</v>
       </c>
       <c r="F28" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="29" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H28" s="24" t="s">
         <v>26</v>
@@ -2910,23 +2908,23 @@
       <c r="I28" s="25"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B29" s="39">
+      <c r="B29" s="36">
         <v>19</v>
       </c>
       <c r="C29" s="23">
         <v>46478</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="39" t="s">
         <v>25</v>
       </c>
       <c r="F29" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="28" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H29" s="24" t="s">
         <v>26</v>
@@ -2935,23 +2933,23 @@
       <c r="J29" s="9"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B30" s="39">
+      <c r="B30" s="36">
         <v>20</v>
       </c>
       <c r="C30" s="23">
         <v>46478</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E30" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="39" t="s">
         <v>25</v>
       </c>
       <c r="F30" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H30" s="24" t="s">
         <v>26</v>
@@ -2960,23 +2958,23 @@
       <c r="J30" s="9"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B31" s="39">
+      <c r="B31" s="36">
         <v>21</v>
       </c>
       <c r="C31" s="23">
         <v>46478</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E31" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="39" t="s">
         <v>25</v>
       </c>
       <c r="F31" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="H31" s="24" t="s">
         <v>26</v>
@@ -2985,23 +2983,23 @@
       <c r="J31" s="9"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B32" s="39">
+      <c r="B32" s="36">
         <v>22</v>
       </c>
       <c r="C32" s="23">
         <v>46478</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="39" t="s">
         <v>25</v>
       </c>
       <c r="F32" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="H32" s="24" t="s">
         <v>26</v>
@@ -3010,23 +3008,23 @@
       <c r="J32" s="9"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B33" s="39">
+      <c r="B33" s="36">
         <v>23</v>
       </c>
       <c r="C33" s="23">
         <v>46478</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E33" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="39" t="s">
         <v>25</v>
       </c>
       <c r="F33" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="26" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H33" s="24" t="s">
         <v>26</v>
@@ -3035,23 +3033,23 @@
       <c r="J33" s="9"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B34" s="39">
+      <c r="B34" s="36">
         <v>24</v>
       </c>
       <c r="C34" s="23">
         <v>46478</v>
       </c>
       <c r="D34" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E34" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="39" t="s">
         <v>25</v>
       </c>
       <c r="F34" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="26" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H34" s="24" t="s">
         <v>26</v>
@@ -3060,23 +3058,23 @@
       <c r="J34" s="9"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B35" s="39">
+      <c r="B35" s="36">
         <v>25</v>
       </c>
       <c r="C35" s="23">
         <v>46478</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E35" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="39" t="s">
         <v>25</v>
       </c>
       <c r="F35" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H35" s="24" t="s">
         <v>26</v>
@@ -3085,878 +3083,880 @@
       <c r="J35" s="9"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B36" s="39">
+      <c r="B36" s="36">
         <v>26</v>
       </c>
       <c r="C36" s="23">
         <v>46174</v>
       </c>
       <c r="D36" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H36" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I36" s="25"/>
+    </row>
+    <row r="37" spans="2:10" ht="108" x14ac:dyDescent="0.4">
+      <c r="B37" s="36">
+        <v>27</v>
+      </c>
+      <c r="C37" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="F37" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="H37" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I37" s="25" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B38" s="36">
+        <v>28</v>
+      </c>
+      <c r="C38" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D38" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="H38" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I38" s="25"/>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B39" s="36">
+        <v>29</v>
+      </c>
+      <c r="C39" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D39" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E39" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H39" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" s="25"/>
+    </row>
+    <row r="40" spans="2:10" ht="66" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="51">
+        <v>30</v>
+      </c>
+      <c r="C40" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D40" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="H40" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I40" s="25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B41" s="36">
+        <v>31</v>
+      </c>
+      <c r="C41" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D41" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="H41" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I41" s="25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" ht="27" x14ac:dyDescent="0.4">
+      <c r="B42" s="36">
+        <v>32</v>
+      </c>
+      <c r="C42" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="H42" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42" s="25"/>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B43" s="51">
+        <v>33</v>
+      </c>
+      <c r="C43" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D43" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E43" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="H43" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I43" s="25"/>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B44" s="36">
+        <v>34</v>
+      </c>
+      <c r="C44" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D44" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="H44" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I44" s="25"/>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B45" s="36">
+        <v>35</v>
+      </c>
+      <c r="C45" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E45" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="H45" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I45" s="25"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B46" s="51">
+        <v>36</v>
+      </c>
+      <c r="C46" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D46" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E46" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="H46" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I46" s="25"/>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B47" s="36">
         <v>37</v>
       </c>
-      <c r="E36" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="26" t="s">
+      <c r="C47" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D47" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E47" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="H47" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I47" s="25"/>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B48" s="36">
+        <v>38</v>
+      </c>
+      <c r="C48" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D48" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="H48" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I48" s="25"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B49" s="51">
+        <v>39</v>
+      </c>
+      <c r="C49" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D49" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E49" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="H49" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I49" s="25"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B50" s="36">
+        <v>40</v>
+      </c>
+      <c r="C50" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D50" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="H50" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I50" s="25"/>
+    </row>
+    <row r="51" spans="1:9" ht="27" x14ac:dyDescent="0.4">
+      <c r="B51" s="36">
+        <v>41</v>
+      </c>
+      <c r="C51" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D51" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E51" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="H51" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I51" s="25"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B52" s="51">
+        <v>42</v>
+      </c>
+      <c r="C52" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D52" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E52" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="H52" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I52" s="46"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B53" s="36">
+        <v>43</v>
+      </c>
+      <c r="C53" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D53" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E53" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="H53" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I53" s="25"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B54" s="36">
+        <v>44</v>
+      </c>
+      <c r="C54" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D54" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E54" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H54" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I54" s="25"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B55" s="51">
+        <v>45</v>
+      </c>
+      <c r="C55" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D55" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="H55" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I55" s="25"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B56" s="36">
+        <v>46</v>
+      </c>
+      <c r="C56" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D56" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E56" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="H56" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I56" s="25"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B57" s="36">
+        <v>47</v>
+      </c>
+      <c r="C57" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D57" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E57" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="H57" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I57" s="25"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B58" s="51">
+        <v>48</v>
+      </c>
+      <c r="C58" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D58" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E58" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="H58" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I58" s="25"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B59" s="36">
+        <v>49</v>
+      </c>
+      <c r="C59" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D59" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E59" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="H59" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I59" s="25"/>
+    </row>
+    <row r="60" spans="1:9" s="21" customFormat="1" ht="27" x14ac:dyDescent="0.4">
+      <c r="B60" s="36">
+        <v>50</v>
+      </c>
+      <c r="C60" s="37">
+        <v>46174</v>
+      </c>
+      <c r="D60" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E60" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="H60" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I60" s="35"/>
+    </row>
+    <row r="61" spans="1:9" s="21" customFormat="1" ht="27" x14ac:dyDescent="0.4">
+      <c r="B61" s="51">
         <v>51</v>
       </c>
-      <c r="H36" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I36" s="25"/>
-    </row>
-    <row r="37" spans="2:10" ht="108" x14ac:dyDescent="0.4">
-      <c r="B37" s="39">
-        <v>27</v>
-      </c>
-      <c r="C37" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E37" s="44" t="s">
+      <c r="C61" s="37">
+        <v>46174</v>
+      </c>
+      <c r="D61" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E61" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="H61" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I61" s="35"/>
+    </row>
+    <row r="62" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B62" s="36">
         <v>52</v>
       </c>
-      <c r="F37" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="26" t="s">
+      <c r="C62" s="37">
+        <v>46174</v>
+      </c>
+      <c r="D62" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="H62" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I62" s="35"/>
+    </row>
+    <row r="63" spans="1:9" s="21" customFormat="1" ht="27" x14ac:dyDescent="0.4">
+      <c r="A63" s="1"/>
+      <c r="B63" s="36">
         <v>53</v>
       </c>
-      <c r="H37" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I37" s="25" t="s">
+      <c r="C63" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D63" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E63" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="H63" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I63" s="25" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B64" s="51">
         <v>54</v>
       </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B38" s="39">
-        <v>28</v>
-      </c>
-      <c r="C38" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D38" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E38" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="26" t="s">
+      <c r="C64" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D64" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E64" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="H64" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I64" s="25"/>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B65" s="36">
         <v>55</v>
       </c>
-      <c r="H38" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I38" s="25"/>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B39" s="39">
-        <v>29</v>
-      </c>
-      <c r="C39" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D39" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E39" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="26" t="s">
+      <c r="C65" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D65" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E65" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="H65" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I65" s="25"/>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B66" s="36">
         <v>56</v>
       </c>
-      <c r="H39" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I39" s="25"/>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B40" s="39">
-        <v>30</v>
-      </c>
-      <c r="C40" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D40" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E40" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="H40" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I40" s="25" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" ht="27" x14ac:dyDescent="0.4">
-      <c r="B41" s="39">
-        <v>31</v>
-      </c>
-      <c r="C41" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D41" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E41" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="H41" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I41" s="25"/>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B42" s="39">
-        <v>32</v>
-      </c>
-      <c r="C42" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D42" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E42" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="H42" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I42" s="25"/>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B43" s="39">
-        <v>33</v>
-      </c>
-      <c r="C43" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D43" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E43" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="H43" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I43" s="25"/>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B44" s="39">
-        <v>34</v>
-      </c>
-      <c r="C44" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D44" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E44" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="H44" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I44" s="25"/>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B45" s="39">
-        <v>35</v>
-      </c>
-      <c r="C45" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D45" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E45" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="H45" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I45" s="25"/>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B46" s="39">
-        <v>36</v>
-      </c>
-      <c r="C46" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D46" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E46" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H46" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I46" s="25"/>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B47" s="39">
-        <v>37</v>
-      </c>
-      <c r="C47" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D47" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E47" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="H47" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I47" s="25"/>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B48" s="39">
-        <v>38</v>
-      </c>
-      <c r="C48" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D48" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E48" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="H48" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I48" s="25"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B49" s="39">
-        <v>39</v>
-      </c>
-      <c r="C49" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D49" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E49" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F49" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="H49" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I49" s="25"/>
-    </row>
-    <row r="50" spans="1:9" ht="27" x14ac:dyDescent="0.4">
-      <c r="B50" s="39">
-        <v>40</v>
-      </c>
-      <c r="C50" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D50" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E50" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="H50" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I50" s="25"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B51" s="39">
-        <v>41</v>
-      </c>
-      <c r="C51" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D51" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E51" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F51" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="H51" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I51" s="25"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B52" s="39">
+      <c r="C66" s="23">
+        <v>46296</v>
+      </c>
+      <c r="D66" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E66" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="C52" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D52" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E52" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F52" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="H52" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I52" s="25"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B53" s="39">
-        <v>43</v>
-      </c>
-      <c r="C53" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D53" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E53" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F53" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="H53" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I53" s="25"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B54" s="39">
-        <v>44</v>
-      </c>
-      <c r="C54" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D54" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E54" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="H54" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I54" s="25"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B55" s="39">
-        <v>45</v>
-      </c>
-      <c r="C55" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D55" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E55" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="H55" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I55" s="25"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B56" s="39">
-        <v>46</v>
-      </c>
-      <c r="C56" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D56" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E56" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H56" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I56" s="25"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B57" s="39">
-        <v>47</v>
-      </c>
-      <c r="C57" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D57" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E57" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="H57" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I57" s="25"/>
-    </row>
-    <row r="58" spans="1:9" s="21" customFormat="1" ht="27" x14ac:dyDescent="0.4">
-      <c r="B58" s="39">
-        <v>48</v>
-      </c>
-      <c r="C58" s="40">
-        <v>46174</v>
-      </c>
-      <c r="D58" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E58" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="H58" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="I58" s="35"/>
-    </row>
-    <row r="59" spans="1:9" s="21" customFormat="1" ht="27" x14ac:dyDescent="0.4">
-      <c r="B59" s="39">
-        <v>49</v>
-      </c>
-      <c r="C59" s="40">
-        <v>46174</v>
-      </c>
-      <c r="D59" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E59" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="H59" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="I59" s="35"/>
-    </row>
-    <row r="60" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="39">
-        <v>50</v>
-      </c>
-      <c r="C60" s="40">
-        <v>46174</v>
-      </c>
-      <c r="D60" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E60" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="F60" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="H60" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="I60" s="35"/>
-    </row>
-    <row r="61" spans="1:9" s="21" customFormat="1" ht="27" x14ac:dyDescent="0.4">
-      <c r="A61" s="1"/>
-      <c r="B61" s="56">
-        <v>51</v>
-      </c>
-      <c r="C61" s="57">
-        <v>46174</v>
-      </c>
-      <c r="D61" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="E61" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" s="55" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="58" t="s">
-        <v>108</v>
-      </c>
-      <c r="H61" s="59" t="s">
-        <v>26</v>
-      </c>
-      <c r="I61" s="60" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B62" s="39">
-        <v>52</v>
-      </c>
-      <c r="C62" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D62" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E62" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="H62" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I62" s="25"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B63" s="39">
-        <v>53</v>
-      </c>
-      <c r="C63" s="23">
-        <v>46174</v>
-      </c>
-      <c r="D63" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E63" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F63" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="H63" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I63" s="25"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B64" s="39">
-        <v>54</v>
-      </c>
-      <c r="C64" s="23">
-        <v>46296</v>
-      </c>
-      <c r="D64" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E64" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="F64" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="H64" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I64" s="25"/>
-    </row>
-    <row r="65" spans="2:10" ht="81" x14ac:dyDescent="0.4">
-      <c r="B65" s="39">
-        <v>55</v>
-      </c>
-      <c r="C65" s="23">
-        <v>46539</v>
-      </c>
-      <c r="D65" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E65" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="F65" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="H65" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I65" s="25" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" ht="81" x14ac:dyDescent="0.4">
-      <c r="B66" s="39">
-        <v>56</v>
-      </c>
-      <c r="C66" s="23">
-        <v>46539</v>
-      </c>
-      <c r="D66" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E66" s="45" t="s">
-        <v>34</v>
-      </c>
       <c r="F66" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="26" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H66" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="I66" s="25" t="s">
-        <v>105</v>
-      </c>
+      <c r="I66" s="25"/>
     </row>
     <row r="67" spans="2:10" ht="81" x14ac:dyDescent="0.4">
-      <c r="B67" s="39">
+      <c r="B67" s="51">
         <v>57</v>
       </c>
       <c r="C67" s="23">
         <v>46539</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E67" s="45" t="s">
-        <v>34</v>
+        <v>45</v>
+      </c>
+      <c r="E67" s="41" t="s">
+        <v>42</v>
       </c>
       <c r="F67" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="26" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H67" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I67" s="25" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" ht="27" x14ac:dyDescent="0.4">
-      <c r="B68" s="39">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" ht="81" x14ac:dyDescent="0.4">
+      <c r="B68" s="36">
         <v>58</v>
       </c>
       <c r="C68" s="23">
-        <v>46174</v>
+        <v>46539</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E68" s="45" t="s">
-        <v>34</v>
+        <v>45</v>
+      </c>
+      <c r="E68" s="41" t="s">
+        <v>42</v>
       </c>
       <c r="F68" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="26" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H68" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I68" s="25" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B69" s="39">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" ht="81" x14ac:dyDescent="0.4">
+      <c r="B69" s="36">
         <v>59</v>
       </c>
       <c r="C69" s="23">
-        <v>46174</v>
+        <v>46539</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E69" s="45" t="s">
-        <v>34</v>
+        <v>45</v>
+      </c>
+      <c r="E69" s="41" t="s">
+        <v>42</v>
       </c>
       <c r="F69" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="26" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="H69" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="I69" s="25"/>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B70" s="39">
+      <c r="I69" s="25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" ht="27" x14ac:dyDescent="0.4">
+      <c r="B70" s="51">
         <v>60</v>
       </c>
       <c r="C70" s="23">
         <v>46174</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E70" s="45" t="s">
-        <v>34</v>
+        <v>45</v>
+      </c>
+      <c r="E70" s="41" t="s">
+        <v>42</v>
       </c>
       <c r="F70" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="26" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H70" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="I70" s="25"/>
+      <c r="I70" s="25" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B71" s="39">
+      <c r="B71" s="36">
         <v>61</v>
       </c>
       <c r="C71" s="23">
-        <v>46539</v>
+        <v>46174</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E71" s="45" t="s">
-        <v>34</v>
+        <v>45</v>
+      </c>
+      <c r="E71" s="41" t="s">
+        <v>42</v>
       </c>
       <c r="F71" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="26" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="H71" s="24" t="s">
         <v>26</v>
@@ -3964,23 +3964,23 @@
       <c r="I71" s="25"/>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B72" s="39">
+      <c r="B72" s="36">
         <v>62</v>
       </c>
       <c r="C72" s="23">
-        <v>46539</v>
+        <v>46174</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E72" s="45" t="s">
-        <v>34</v>
+        <v>45</v>
+      </c>
+      <c r="E72" s="41" t="s">
+        <v>42</v>
       </c>
       <c r="F72" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="26" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="H72" s="24" t="s">
         <v>26</v>
@@ -3988,23 +3988,23 @@
       <c r="I72" s="25"/>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B73" s="39">
+      <c r="B73" s="51">
         <v>63</v>
       </c>
       <c r="C73" s="23">
         <v>46539</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E73" s="45" t="s">
-        <v>34</v>
+        <v>45</v>
+      </c>
+      <c r="E73" s="41" t="s">
+        <v>42</v>
       </c>
       <c r="F73" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="26" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H73" s="24" t="s">
         <v>26</v>
@@ -4012,47 +4012,47 @@
       <c r="I73" s="25"/>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B74" s="39">
+      <c r="B74" s="36">
         <v>64</v>
       </c>
       <c r="C74" s="23">
-        <v>46174</v>
+        <v>46539</v>
       </c>
       <c r="D74" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E74" s="45" t="s">
-        <v>34</v>
+        <v>45</v>
+      </c>
+      <c r="E74" s="41" t="s">
+        <v>42</v>
       </c>
       <c r="F74" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="26" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H74" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="I74" s="32"/>
+      <c r="I74" s="25"/>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B75" s="39">
+      <c r="B75" s="36">
         <v>65</v>
       </c>
       <c r="C75" s="23">
-        <v>46174</v>
+        <v>46539</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E75" s="45" t="s">
-        <v>34</v>
+        <v>45</v>
+      </c>
+      <c r="E75" s="41" t="s">
+        <v>42</v>
       </c>
       <c r="F75" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="26" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H75" s="24" t="s">
         <v>26</v>
@@ -4060,89 +4060,113 @@
       <c r="I75" s="25"/>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B76" s="39">
+      <c r="B76" s="51">
         <v>66</v>
       </c>
       <c r="C76" s="23">
         <v>46174</v>
       </c>
       <c r="D76" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E76" s="45" t="s">
-        <v>34</v>
+        <v>45</v>
+      </c>
+      <c r="E76" s="41" t="s">
+        <v>42</v>
       </c>
       <c r="F76" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="26" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="H76" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="I76" s="25"/>
-    </row>
-    <row r="77" spans="2:10" s="21" customFormat="1" ht="40.5" x14ac:dyDescent="0.4">
-      <c r="B77" s="39">
+      <c r="I76" s="32"/>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B77" s="36">
         <v>67</v>
       </c>
-      <c r="C77" s="40">
+      <c r="C77" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D77" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E77" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F77" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="H77" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I77" s="25"/>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B78" s="36">
+        <v>68</v>
+      </c>
+      <c r="C78" s="23">
+        <v>46174</v>
+      </c>
+      <c r="D78" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E78" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F78" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="H78" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I78" s="25"/>
+    </row>
+    <row r="79" spans="2:10" s="21" customFormat="1" ht="41.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B79" s="58">
+        <v>69</v>
+      </c>
+      <c r="C79" s="52">
         <v>46539</v>
       </c>
-      <c r="D77" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E77" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="F77" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="H77" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="I77" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="J77" s="31"/>
-    </row>
-    <row r="78" spans="2:10" s="21" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B78" s="53">
-        <v>68</v>
-      </c>
-      <c r="C78" s="41">
-        <v>46174</v>
-      </c>
-      <c r="D78" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="E78" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="F78" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="H78" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="I78" s="38"/>
+      <c r="D79" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E79" s="54" t="s">
+        <v>42</v>
+      </c>
+      <c r="F79" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="H79" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="I79" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="J79" s="31"/>
     </row>
   </sheetData>
-  <autoFilter ref="A10:J78" xr:uid="{A46FDE0A-2F10-41C6-B18F-E0480B0F45EB}"/>
+  <autoFilter ref="A10:J79" xr:uid="{A46FDE0A-2F10-41C6-B18F-E0480B0F45EB}"/>
   <mergeCells count="3">
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B1:I1"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
-  <conditionalFormatting sqref="F11:F78 H11:H78">
+  <conditionalFormatting sqref="F11:F79 H11:H79">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"☑"</formula>
     </cfRule>
@@ -4157,7 +4181,7 @@
           <x14:formula1>
             <xm:f>リスト!$A$1:$A$2</xm:f>
           </x14:formula1>
-          <xm:sqref>H11:H78 F11:F78</xm:sqref>
+          <xm:sqref>F11:F79 H11:H79</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4175,12 +4199,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" s="17" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -4209,15 +4233,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100DEA2635F732F464D88FD0617849E9F69" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="07a4d2faf2f8f28b7a2f551c9ec83f9e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="33f003c0-0d95-44a8-96ef-b6b435aaba2f" xmlns:ns3="263dbbe5-076b-4606-a03b-9598f5f2f35a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8a3684643123949165adbe6bede2192a" ns2:_="" ns3:_="">
     <xsd:import namespace="33f003c0-0d95-44a8-96ef-b6b435aaba2f"/>
@@ -4450,32 +4465,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D84A4EC1-9062-4FB9-98E6-03C16F8C3709}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="33f003c0-0d95-44a8-96ef-b6b435aaba2f"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
-    <ds:schemaRef ds:uri="33f003c0-0d95-44a8-96ef-b6b435aaba2f"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{002E9B92-A2CF-4424-BC7F-395BCE423FC6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AFB7EBC-F48A-4966-837D-66F1F854E821}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4492,4 +4508,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{002E9B92-A2CF-4424-BC7F-395BCE423FC6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>